--- a/documentazione/test/TestAntQuest.xlsx
+++ b/documentazione/test/TestAntQuest.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="23970" windowHeight="10545" tabRatio="845" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="23970" windowHeight="10560" tabRatio="845" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="332">
   <si>
     <t>Nome Progetto</t>
   </si>
@@ -230,9 +230,6 @@
     <t>aggiungere altri dati richiesti</t>
   </si>
   <si>
-    <t>registrazione anche senza maiuscole</t>
-  </si>
-  <si>
     <t xml:space="preserve">modifica anche i dati inseriti nello step1 </t>
   </si>
   <si>
@@ -285,9 +282,6 @@
   </si>
   <si>
     <t>verificare la funzionalita logout su html di Ant Quests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://localhost:8080/homeStud/doQuestionario?quest-select=1     (doQuest.html)    </t>
   </si>
   <si>
     <t xml:space="preserve">http://localhost:8080/homeStud/doQuestionario?quest-select=1  </t>
@@ -490,12 +484,6 @@
     <t>messaggio di errore che comunica l'inserimento errato di password e/o email</t>
   </si>
   <si>
-    <t>messaggio di errore che comunica l'inserimento errato di password e/o email + campo vuoto nell'email</t>
-  </si>
-  <si>
-    <t>messaggio di errore che comunica l'inserimento errato di password e/o email + campo vuoto nella password</t>
-  </si>
-  <si>
     <t>TC_AQ_Login_004</t>
   </si>
   <si>
@@ -568,9 +556,6 @@
   <si>
     <t>1. non modificare i dati presenti                  2. compilare tutti gli altri campi:                     -numero di telefono verificando il num min e max valido                              - data nascita verificando che non può esserci la data futura                              -cap  verificando il num min e max valido                                -provincia verificando le lettere min e max valide                              - nuova password verificando requisiti   -conferma password verificando requisiti e uguale alla nuova password
 3. cliccare sul bottone registrati</t>
-  </si>
-  <si>
-    <t>i campi sono tutti obbligatori escluso il cap                          nella password non c'è il requisito inserimento simboli</t>
   </si>
   <si>
     <t xml:space="preserve">1.Passare il mouse sull'occhietto password e verificare se viene visualizzata                     2. Cliccare sull'occhietto password e verificare se viene visualizzata </t>
@@ -608,16 +593,7 @@
 ant                                            cognome:                              quest</t>
   </si>
   <si>
-    <t>Se i dati inseriti rispettano i requisiti, una volta cliccato su continuare registrazione, si potre continuare ad inserire altri dati e modificare quelli correnti</t>
-  </si>
-  <si>
     <t>messaggio campo vuoto</t>
-  </si>
-  <si>
-    <t>messaggio email errata</t>
-  </si>
-  <si>
-    <t>messaggio registrazione avvenuta con successo</t>
   </si>
   <si>
     <t>lista quest svolti: titolo,data,  punteggio, tempo, azioni con pdf</t>
@@ -646,9 +622,6 @@
     <t>ritorno alla pagina login</t>
   </si>
   <si>
-    <t>Se l'utente è registrato login                                         Se l'utente non è registrato errore</t>
-  </si>
-  <si>
     <t>link della pagina corrente selezionato</t>
   </si>
   <si>
@@ -716,9 +689,6 @@
   </si>
   <si>
     <t xml:space="preserve"> fine sessione + ritorno al login</t>
-  </si>
-  <si>
-    <t>nella password non c'è il requisito simboli    +             i campi sono tutti obbligatori escluso il cap</t>
   </si>
   <si>
     <t>verificare la sessione profilo studente di Ant Quests</t>
@@ -765,9 +735,6 @@
 3. cliccare sul bottone chiudi 4.cliccare sul pulsante vedi di questionario          5. cliccare sul pulsante pdf e verificare l'apertura file</t>
   </si>
   <si>
-    <t>1. cliccare sul pulsante pdf e verificare l'apertura file 2. cliccare ul pulsante chiudi 3. verificare dati presenti in tabella: utente,data, titolo,categoria tempo, punteggio</t>
-  </si>
-  <si>
     <t>TC_AQ_Home_Admin_005</t>
   </si>
   <si>
@@ -778,9 +745,6 @@
   </si>
   <si>
     <t xml:space="preserve">1. cliccare su logout                       2. verificare se fine sessione + ritorno al login           </t>
-  </si>
-  <si>
-    <t>non scade la sessione all'admin</t>
   </si>
   <si>
     <t>verificare la funzionalità studenti admin di Ant Quests</t>
@@ -805,11 +769,6 @@
 3. verificare l'aggiornamento in tabella per ogni campo compilato   4. cambiare ruolo da studente a guest e viceversa 5. selezionare altro corso </t>
   </si>
   <si>
-    <t xml:space="preserve">1. cliccare su filtri ricerca
-2. scegliere ruolo
-3. verificare l'aggiornamento in tabella                      4. cambiare ruolo da studente a guest e viceversa     5. resettare e iniziare la compilazione dal corso 5.  </t>
-  </si>
-  <si>
     <t xml:space="preserve">1. cliccare sul pulsante vedi di questionari, cliccare su pdf e verificare l'apertura file        2. verificare dati presenti in tabella: utente,data, titolo,categoria tempo, punteggio 3. cliccare sul pulsante chiudi </t>
   </si>
   <si>
@@ -856,9 +815,6 @@
   </si>
   <si>
     <t>cliccando su chiudi annullerà tutto, cliccando su salva il nuovo corso sarà presente in tabella</t>
-  </si>
-  <si>
-    <t>i campi nome corso, data inizio e data fine non possono essere vuoti</t>
   </si>
   <si>
     <t xml:space="preserve"> modifica tutti i dati corso</t>
@@ -1025,9 +981,6 @@
     <t>1. cliccare sul pulsante aggiungi nuovo studente          2. inserisci nome , cognome ed email                   3. cliccare sul pulsante chiudi      4. ripetere l'operazione fino al punto 2 e cliccare su salva</t>
   </si>
   <si>
-    <t>i campi nome , cognome ed emailnon possono essere vuoti</t>
-  </si>
-  <si>
     <t xml:space="preserve">questionari vedi </t>
   </si>
   <si>
@@ -1051,7 +1004,111 @@
     <t>le domande possono essere modificate, appaiono i messaggi di successo e vengono salvate</t>
   </si>
   <si>
-    <t>Rossella -chrome</t>
+    <t>messaggio che comunica  campo vuoto nell'email</t>
+  </si>
+  <si>
+    <t>messaggio che comunica  campo vuoto nella password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visualizzazione password </t>
+  </si>
+  <si>
+    <t>registrazione anche senza maiuscole nel nome e cognome</t>
+  </si>
+  <si>
+    <t>Se i dati inseriti rispettano i requisiti, una volta cliccato su continuare registrazione, si può continuare ad inserire altri dati e modificare quelli correnti. C'è un messaggio nel campo email con i requisiti da rispettare e se è accettabile</t>
+  </si>
+  <si>
+    <t>messaggio email errata, chiede di inserire un'email valida</t>
+  </si>
+  <si>
+    <t>modifiche dati inseriti precedentemente+ messaggio campo vuoto</t>
+  </si>
+  <si>
+    <t>messaggio registrazione avvenuta con successo per dati inseriti correttamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non accetta data futura e messaggi per requisiti da rispettare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">messaggio registrazione avvenuta con successo se dati inseriti rispettano i requisiti, altrimenti no rimane sulla pagina  comunicando di inserire il formato richiesto nei campi inseriti in modo sbagliato.  . non accetta data futura e messaggi per requisiti da rispettare </t>
+  </si>
+  <si>
+    <t>apertura pdf</t>
+  </si>
+  <si>
+    <t>non apre il formato pdf</t>
+  </si>
+  <si>
+    <t>non seleziona il link della pagina corrente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t>concludi e pulisci ko + pulsanti home e logout ok</t>
+  </si>
+  <si>
+    <t>Rossella -chrome- 04/09/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concludi e pulisci ko </t>
+  </si>
+  <si>
+    <t>nella password non c'è il requisito simboli    +             i campi sono tutti obbligatori escluso il cap+ blocco input formato numero, provincia e telefono  EMAIL NON VIENE MODIFICATA</t>
+  </si>
+  <si>
+    <t>sia per studente+ guest+ admin  MANCA MSG PER RECUPERO PASSWORD</t>
+  </si>
+  <si>
+    <t>1. cliccare sul pulsante pdf e verificare l'apertura file 2. cliccare sul pulsante chiudi 3. verificare dati presenti in tabella: utente,data, titolo,categoria tempo, punteggio</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. cliccare su filtri ricerca
+2. scegliere ruolo
+3. verificare l'aggiornamento in tabella                      4. cambiare ruolo da studente a guest e viceversa     5. resettare e iniziare la compilazione dal corso </t>
+  </si>
+  <si>
+    <t>i campi nome corso, data inizio e data fine non possono essere vuoti. NON C'è POSSIBILITà DI ELIMINARE DEFINITIVAMENTE IL CORSO</t>
+  </si>
+  <si>
+    <t>COLORE PULSANTE CONFERMA AGGIUNTA STUDENTE</t>
+  </si>
+  <si>
+    <t>COLORE MSG AVVENUTA CREAZIONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.blocco  aggiungi finchè non si scrive la domanda ok,pulisci ok. 2.aggiungi domanda con risposte vuote o senza ko, pulisci ok.è possibile aggiungere risposte tutte errate  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">switch ok sia con frecce che bottone domande      </t>
+  </si>
+  <si>
+    <t>senza .it/.com va allo step successivo. nonostante messaggi requisiti comunica dati non validi + registra con nome e congnome di una sola lettera</t>
+  </si>
+  <si>
+    <t>scade la sessione + verifica se ha il permesso all'admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> verifica se ha il permesso/ruolo</t>
+  </si>
+  <si>
+    <t>verifica se ha il permesso/ruolo</t>
+  </si>
+  <si>
+    <t>Rossella -chrome - 04/09/24</t>
+  </si>
+  <si>
+    <t>Rossella -chrome-04/09/24</t>
+  </si>
+  <si>
+    <t>Rossella -chrome 04/09/24</t>
+  </si>
+  <si>
+    <t>i campi nome , cognome ed emailnon possono essere vuoti.  REQUISITI EMAIL. Salva senza inserire .it/.com</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1145,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1098,6 +1155,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1203,7 +1266,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1221,12 +1284,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1309,9 +1366,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1340,6 +1394,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -1653,127 +1728,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1">
-      <c r="A2" s="16" t="s">
+      <c r="C1" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1">
+      <c r="A2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="15" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
-      <c r="A3" s="17" t="s">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" s="17" t="s">
+      <c r="I3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>312</v>
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="63.75" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
+        <v>144</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
       <c r="K4" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="86.25" customHeight="1">
-      <c r="A5" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="131.25" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>17</v>
@@ -1782,100 +1860,109 @@
         <v>18</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
+        <v>145</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
       <c r="K5" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
+        <v>315</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="75">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
+        <v>145</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
+        <v>159</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="75">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="75">
+      <c r="A8" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="90">
-      <c r="A8" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>17</v>
@@ -1884,66 +1971,72 @@
         <v>23</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="75">
+      <c r="A9" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="90">
-      <c r="A9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
+        <v>297</v>
+      </c>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
       <c r="K9" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="90">
-      <c r="A10" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="75">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>17</v>
@@ -1952,32 +2045,35 @@
         <v>24</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
+        <v>297</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
       <c r="K10" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="105">
-      <c r="A11" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="75">
+      <c r="A11" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>17</v>
@@ -1986,91 +2082,94 @@
         <v>25</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
+        <v>298</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
       <c r="K11" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L11" s="24" t="s">
-        <v>221</v>
+        <v>159</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="105">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>158</v>
+      <c r="B12" s="22" t="s">
+        <v>154</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>139</v>
+        <v>299</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>137</v>
       </c>
       <c r="F12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>221</v>
+        <v>159</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="94.5" customHeight="1">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>158</v>
+      <c r="B13" s="22" t="s">
+        <v>154</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="L13" s="24" t="s">
-        <v>221</v>
+        <v>159</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="7"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2093,92 +2192,92 @@
     <col min="8" max="8" width="23.140625" style="5" customWidth="1"/>
     <col min="9" max="9" width="14.140625" style="5" customWidth="1"/>
     <col min="10" max="10" width="8.28515625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" style="4" customWidth="1"/>
     <col min="12" max="12" width="15.42578125" customWidth="1"/>
     <col min="14" max="14" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1">
-      <c r="A2" s="26" t="s">
+      <c r="C1" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1">
+      <c r="A2" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="30"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
-      <c r="A3" s="17" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="28"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" s="17" t="s">
+      <c r="I3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="195">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="28" t="s">
-        <v>161</v>
+      <c r="B4" s="26" t="s">
+        <v>157</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>57</v>
@@ -2187,64 +2286,72 @@
         <v>58</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
+        <v>301</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
       <c r="K4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="105">
-      <c r="A5" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="39" customFormat="1" ht="195">
+      <c r="A5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
+      <c r="E5" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="120">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>161</v>
+      <c r="B6" s="26" t="s">
+        <v>157</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>55</v>
@@ -2253,30 +2360,33 @@
         <v>51</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
+        <v>173</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="3" customFormat="1" ht="105">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>161</v>
+      <c r="B7" s="27" t="s">
+        <v>157</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>54</v>
@@ -2285,31 +2395,33 @@
         <v>52</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
+        <v>174</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="N7" s="38"/>
+      <c r="L7" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="N7" s="36" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="75">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>162</v>
+      <c r="B8" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>60</v>
@@ -2318,27 +2430,30 @@
         <v>63</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>181</v>
+      <c r="H8" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
+        <v>65</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="165">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="24" t="s">
-        <v>162</v>
+      <c r="B9" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>61</v>
@@ -2347,90 +2462,103 @@
         <v>62</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="390">
-      <c r="A10" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="39" customFormat="1" ht="390">
+      <c r="A10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>221</v>
+      <c r="E10" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N10" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="150">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>160</v>
+      <c r="B11" s="22" t="s">
+        <v>156</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="L11" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="60">
+      <c r="A12" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="L11" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="60">
-      <c r="A12" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>221</v>
+      <c r="L12" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2462,43 +2590,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
+      <c r="C1" s="40" t="s">
+        <v>262</v>
       </c>
       <c r="D1" s="5"/>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="11" customFormat="1">
-      <c r="A2" s="31" t="s">
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="9" customFormat="1">
+      <c r="A2" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="37"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="12"/>
-      <c r="N2" s="35"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
-      <c r="A3" s="17" t="s">
+      <c r="D2" s="35"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="35"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="10"/>
+      <c r="N2" s="33"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -2507,392 +2635,417 @@
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="90">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:14" s="39" customFormat="1" ht="90">
+      <c r="A4" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
+      <c r="D4" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="I4" s="26"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="75">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>83</v>
+      <c r="B5" s="22" t="s">
+        <v>82</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="39" customFormat="1" ht="75">
+      <c r="A6" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="I6" s="38"/>
+      <c r="K6" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N6" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="55" customFormat="1" ht="60">
+      <c r="A7" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="42" customFormat="1" ht="75">
-      <c r="A6" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="I6" s="41"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="N6" s="40"/>
-    </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" ht="60">
-      <c r="A7" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="36" t="s">
+      <c r="D7" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="54"/>
+      <c r="H7" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="I7" s="53" t="s">
+        <v>252</v>
+      </c>
+      <c r="K7" s="53"/>
+      <c r="L7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N7" s="54" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="10" customFormat="1" ht="60">
+      <c r="A8" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="28"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="28"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="1:14" ht="90">
+      <c r="A9" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="N7" s="38"/>
-    </row>
-    <row r="8" spans="1:14" s="12" customFormat="1" ht="60">
-      <c r="A8" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="30"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="N8" s="14"/>
-    </row>
-    <row r="9" spans="1:14" ht="90">
-      <c r="A9" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>203</v>
-      </c>
       <c r="F9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="17"/>
       <c r="H9" s="7" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>221</v>
+      <c r="K9" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="120">
-      <c r="A10" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>78</v>
+      <c r="A10" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="19"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="75">
-      <c r="A11" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>78</v>
+      <c r="K10" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="60">
+      <c r="A11" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="19"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="7" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="39" t="s">
+      <c r="K11" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="39" customFormat="1" ht="195">
+      <c r="A12" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="I12" s="26"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N12" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="105">
+      <c r="A13" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="195">
-      <c r="A12" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="E13" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="75">
+      <c r="A14" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D14" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="39" customFormat="1" ht="60">
+      <c r="A15" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="105">
-      <c r="A13" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="75">
-      <c r="A14" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="D15" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="60">
-      <c r="A15" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L15" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>266</v>
+      <c r="F15" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="I15" s="38"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N15" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2902,19 +3055,15 @@
       <c r="F17" s="7"/>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="34"/>
+      <c r="A42" s="32"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="K9" r:id="rId2"/>
-    <hyperlink ref="A8" r:id="rId3"/>
-    <hyperlink ref="K10" r:id="rId4"/>
-    <hyperlink ref="K11" r:id="rId5"/>
-    <hyperlink ref="K12" r:id="rId6"/>
+    <hyperlink ref="A8" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2938,42 +3087,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
+      <c r="C1" s="40" t="s">
+        <v>262</v>
       </c>
       <c r="D1" s="5"/>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1" ht="30">
-      <c r="A2" s="30" t="s">
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1" ht="30">
+      <c r="A2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="30"/>
-      <c r="K2" s="14"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
+      <c r="D2" s="28"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="28"/>
+      <c r="K2" s="12"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -2982,200 +3131,215 @@
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>312</v>
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="409.5">
-      <c r="A4" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>223</v>
+      <c r="A4" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>213</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="195">
+      <c r="A5" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="60">
+      <c r="A6" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>225</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="195">
-      <c r="A5" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="60">
-      <c r="A6" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="K6" s="4"/>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="60">
-      <c r="A7" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>223</v>
+      <c r="A7" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>213</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="K7" s="4"/>
-      <c r="L7" s="24" t="s">
-        <v>221</v>
+      <c r="L7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="75">
-      <c r="A8" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>223</v>
+      <c r="A8" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>213</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="39" customFormat="1" ht="60">
+      <c r="A9" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="60">
-      <c r="A9" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>266</v>
+      <c r="F9" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="I9" s="38"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N9" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3205,43 +3369,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
+      <c r="C1" s="40" t="s">
+        <v>262</v>
       </c>
       <c r="D1" s="5"/>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1">
-      <c r="A2" s="30" t="s">
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1">
+      <c r="A2" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="14"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
+      <c r="D2" s="28"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="12"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -3250,175 +3414,190 @@
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>312</v>
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="255">
-      <c r="A4" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>302</v>
+      <c r="A4" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>288</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="180">
+      <c r="A5" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="75">
+      <c r="A6" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="180">
-      <c r="A5" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="75">
-      <c r="A6" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K6" s="4"/>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="75">
-      <c r="A7" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>302</v>
+      <c r="A7" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>288</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="39" customFormat="1" ht="75">
+      <c r="A8" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="60">
-      <c r="A8" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
+      <c r="F8" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N8" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3447,305 +3626,328 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1">
-      <c r="A2" s="30" t="s">
+      <c r="C1" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1">
+      <c r="A2" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="195">
-      <c r="A4" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="39" customFormat="1" ht="195">
+      <c r="A4" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="195">
+      <c r="A5" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="195">
-      <c r="A5" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="39" customFormat="1" ht="180">
+      <c r="A6" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N6" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="39" customFormat="1" ht="409.5">
+      <c r="A7" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="180">
-      <c r="A6" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D7" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="K7" s="38"/>
+      <c r="L7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N7" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="210">
+      <c r="A8" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>303</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41" t="s">
-        <v>244</v>
-      </c>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="409.5">
-      <c r="A7" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="E7" s="49" t="s">
-        <v>246</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40" t="s">
-        <v>247</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="210">
-      <c r="A8" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="K8" s="4"/>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="75">
-      <c r="A9" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>236</v>
+      <c r="A9" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>224</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K9" s="4"/>
-      <c r="L9" s="24" t="s">
-        <v>221</v>
+      <c r="L9" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="75">
-      <c r="A10" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>236</v>
+      <c r="A10" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>224</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="39" customFormat="1" ht="60">
+      <c r="A11" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="60">
-      <c r="A11" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L11" s="24" t="s">
-        <v>221</v>
+      <c r="F11" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="K11" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N11" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3792,332 +3994,363 @@
     <col min="7" max="7" width="15" style="5" customWidth="1"/>
     <col min="8" max="8" width="21.85546875" style="5" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="15.5703125" customWidth="1"/>
     <col min="14" max="14" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1">
-      <c r="A2" s="30" t="s">
+      <c r="C1" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1">
+      <c r="A2" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="150">
-      <c r="A4" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="24" t="s">
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="39" customFormat="1" ht="150">
+      <c r="A4" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="225">
+      <c r="A5" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="210">
+      <c r="A6" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="409.5">
+      <c r="A7" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="240">
+      <c r="A8" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="210">
+      <c r="A9" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="225">
-      <c r="A5" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="210">
-      <c r="A6" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="409.5">
-      <c r="A7" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>246</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="240">
-      <c r="A8" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="F9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="75">
+      <c r="A10" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="210">
-      <c r="A9" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="75">
-      <c r="A10" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="I10" s="4"/>
       <c r="K10" s="4"/>
-      <c r="L10" s="24" t="s">
-        <v>221</v>
+      <c r="L10" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="75">
-      <c r="A11" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="39" customFormat="1" ht="75">
+      <c r="A11" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="37"/>
+      <c r="H11" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="K11" s="38"/>
+      <c r="L11" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N11" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="39" customFormat="1" ht="60">
+      <c r="A12" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="60">
-      <c r="A12" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>221</v>
+      <c r="F12" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="K12" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N12" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4141,252 +4374,274 @@
     <col min="8" max="8" width="22.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" style="5" customWidth="1"/>
     <col min="10" max="10" width="8.42578125" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" style="5" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1">
-      <c r="A2" s="47" t="s">
+      <c r="C1" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1">
+      <c r="A2" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="N2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>76</v>
+      <c r="I3" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="195">
-      <c r="A4" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="4" spans="1:14" s="39" customFormat="1" ht="195">
+      <c r="A4" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="I4" s="43"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="39" customFormat="1" ht="300">
+      <c r="A5" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="I5" s="37"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="165">
+      <c r="A6" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="I4" s="46"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="300">
-      <c r="A5" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D6" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="75">
+      <c r="A7" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="165">
-      <c r="A6" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="75">
-      <c r="A7" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="24" t="s">
-        <v>221</v>
+        <v>206</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="75">
-      <c r="A8" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>267</v>
+      <c r="A8" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>253</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="60">
-      <c r="A9" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>221</v>
+        <v>184</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="39" customFormat="1" ht="60">
+      <c r="A9" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="I9" s="37"/>
+      <c r="K9" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N9" s="37" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4453,46 +4708,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1">
-      <c r="A2" s="30" t="s">
+      <c r="C1" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1">
+      <c r="A2" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="34" t="s">
+      <c r="D2" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14" t="s">
+      <c r="F2" s="12"/>
+      <c r="G2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="N2" s="30"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
+      <c r="H2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="N2" s="28"/>
+    </row>
+    <row r="3" spans="1:14" ht="45">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -4501,238 +4756,251 @@
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>312</v>
+      <c r="L3" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="180">
-      <c r="A4" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>287</v>
+      <c r="A4" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>273</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="I4" s="43"/>
+      <c r="K4" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="50" customFormat="1" ht="390">
+      <c r="A5" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="51"/>
+      <c r="H5" s="48" t="s">
+        <v>294</v>
+      </c>
+      <c r="K5" s="48" t="s">
+        <v>322</v>
+      </c>
+      <c r="L5" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="N5" s="48" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="225">
+      <c r="A6" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="225">
+      <c r="A7" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="I4" s="46"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="390">
-      <c r="A5" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="225">
-      <c r="A6" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="225">
-      <c r="A7" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I7" s="25"/>
+        <v>292</v>
+      </c>
+      <c r="I7" s="23"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="24" t="s">
-        <v>221</v>
+      <c r="L7" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="60">
-      <c r="A8" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>287</v>
+      <c r="A8" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>273</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K8" s="4"/>
-      <c r="L8" s="24" t="s">
-        <v>221</v>
+      <c r="L8" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="60">
-      <c r="A9" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>287</v>
+      <c r="A9" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>273</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="22" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="39" customFormat="1" ht="60">
+      <c r="A10" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="60">
-      <c r="A10" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>221</v>
+      <c r="F10" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="K10" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N10" s="38" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
